--- a/public/exports/28856075.xlsx
+++ b/public/exports/28856075.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:O39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -24,55 +24,65 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ejerskab</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primær registreret ejer</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Geografisk kommunekode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t xml:space="preserve">Adresse</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Postnr.</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Energimærkningsfirma</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -91,42 +101,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Halvejen 20</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">5482154</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>678</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -134,10 +144,20 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -156,42 +176,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Halvejen 22B</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">5482154</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>644</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -199,10 +219,20 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -221,42 +251,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Havnegade 1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">734262, 7828151</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>342</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -264,10 +294,20 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -286,42 +326,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Havnegade 11</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">734264, 5481257</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">60</t>
         </is>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>711</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -329,10 +369,20 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -351,42 +401,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Havnepladsen 2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">734268, 5481265</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">58</t>
         </is>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>397</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -394,10 +444,20 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -416,42 +476,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Markgade 1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">5480347</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>649</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -459,10 +519,20 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,42 +551,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Markgade 1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">5480347</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>365</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -524,10 +594,20 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -546,42 +626,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Markgade 1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">5480347</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>785</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -589,10 +669,20 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -611,42 +701,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Møllevejen 40</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">5482154</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>332</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -654,10 +744,20 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -676,42 +776,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Pakhusvej 3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">734295, 7828151</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>297</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -719,10 +819,20 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -741,42 +851,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Reberbanen 58</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">100015361</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>491</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -784,10 +894,20 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -806,42 +926,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Skolegade 28</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">5480375</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>352</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -849,10 +969,20 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -871,42 +1001,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">St. Rise Skolevej 1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">734316, 5072879</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>1062</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -914,10 +1044,20 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -936,42 +1076,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tordenskjoldsgade 20</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">5481018</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>718</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -979,10 +1119,20 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1001,42 +1151,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vestergade 48C</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">734281, 5482498</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>376</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -1044,10 +1194,20 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1066,42 +1226,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vestergade 48C</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">734281, 5482498</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>326</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -1109,10 +1269,20 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,42 +1301,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vitsø 1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">5985</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">734314, 5074611</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>664</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -1174,10 +1344,20 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1196,42 +1376,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vråvejen 16C</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">734335, 7403913</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>1201</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -1239,10 +1419,20 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1261,53 +1451,63 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vestergade 1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">7125841</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>352</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">200031208</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Rambøll Danmark A/S (Kolding)</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-05-06</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1326,53 +1526,63 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vestergade 32</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">5481279</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>1454</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">200047026</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Rambøll Danmark A/S (Kolding)</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-03-21</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1391,53 +1601,63 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Søndergade 16B</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">8279514</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>397</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">200048884</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Rambøll Danmark A/S (Odense)</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-05-06</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1456,53 +1676,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Halvejen 24</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">5482154</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>5417</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">311519677</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-12</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1521,53 +1751,63 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Statene 2</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">1355910</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>3366</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">311558148</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1586,53 +1826,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Statene 6</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">5503780</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>632</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">311558150</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1651,53 +1901,63 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Sygehusvejen 33B</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">5503798</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>315</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t xml:space="preserve">311558147</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1716,53 +1976,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ellenet 10</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">5482816</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>3153</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t xml:space="preserve">311614100</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,53 +2051,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gasværksvej 6</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">5481241</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>393</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t xml:space="preserve">311614197</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1846,53 +2126,63 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ellenet 10</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">5482816</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H29">
+      <c r="J29">
         <v>318</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t xml:space="preserve">311620606</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1911,53 +2201,63 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">St. Rise Skolevej 3</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">5072876</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>915</v>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311650588</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311650629</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1976,53 +2276,63 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">St. Rise Skolevej 3</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">5072876</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>1222</v>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311650588</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311650619</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2041,53 +2351,63 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">St. Rise Skolevej 3</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve">5072876</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H32">
+      <c r="J32">
         <v>257</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311650588</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311650606</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2106,53 +2426,63 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ærøskøbing Havn 4</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">5503437</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>431</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t xml:space="preserve">311652357</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2171,53 +2501,63 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ærøskøbing Havn 4A</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve">5503437</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>717</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t xml:space="preserve">311652357</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2236,53 +2576,63 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Statene 40</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">5503715</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H35">
+      <c r="J35">
         <v>355</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t xml:space="preserve">311760253</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Energimanden ApS</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-17</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2301,53 +2651,63 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Statene 42</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">5503715</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>1616</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t xml:space="preserve">311760254</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Energimanden ApS</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-17</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2366,53 +2726,63 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Statene 44</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">5970</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">5503715</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H37">
+      <c r="J37">
         <v>837</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t xml:space="preserve">311760258</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Energimanden ApS</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-17</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,53 +2801,63 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Halvejen 22</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve">734278, 5482154</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>1078</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t xml:space="preserve">311766361</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Energimanden ApS</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-06-13</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2496,59 +2876,69 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">492</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærø Kommune</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kirkestræde 23</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">5960</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">5480514</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>284</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t xml:space="preserve">311877761</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-21</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M39"/>
+  <autoFilter ref="A1:O39"/>
 </worksheet>
 </file>
--- a/public/exports/28856075.xlsx
+++ b/public/exports/28856075.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2539,12 +2539,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652357</t>
+          <t xml:space="preserve">311652376</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">

--- a/public/exports/28856075.xlsx
+++ b/public/exports/28856075.xlsx
@@ -2539,12 +2539,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652376</t>
+          <t xml:space="preserve">311652357</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M34" t="inlineStr">
